--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BD9E99-86C1-463C-B94E-B9B0D29E1E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B42FC4-CD42-47D8-998B-657CDA2C8453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="-15405" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9720" yWindow="-13470" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -783,10 +783,10 @@
       </c>
       <c r="E2" s="1">
         <f>VLOOKUP(F2,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B42FC4-CD42-47D8-998B-657CDA2C8453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3247E6B-7F17-4606-B9BF-9E123A9F7A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="-13470" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -399,51 +399,19 @@
         </row>
         <row r="20">
           <cell r="A20">
+            <v>2299</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>{0}[{1}]</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
             <v>2300</v>
           </cell>
-          <cell r="B20" t="str">
+          <cell r="B21" t="str">
             <v>巻物</v>
           </cell>
-        </row>
-        <row r="21">
-          <cell r="A21"/>
-          <cell r="B21"/>
-        </row>
-        <row r="22">
-          <cell r="A22"/>
-          <cell r="B22"/>
-        </row>
-        <row r="23">
-          <cell r="A23"/>
-          <cell r="B23"/>
-        </row>
-        <row r="24">
-          <cell r="A24"/>
-          <cell r="B24"/>
-        </row>
-        <row r="25">
-          <cell r="A25"/>
-          <cell r="B25"/>
-        </row>
-        <row r="26">
-          <cell r="A26"/>
-          <cell r="B26"/>
-        </row>
-        <row r="27">
-          <cell r="A27"/>
-          <cell r="B27"/>
-        </row>
-        <row r="28">
-          <cell r="A28"/>
-          <cell r="B28"/>
-        </row>
-        <row r="29">
-          <cell r="A29"/>
-          <cell r="B29"/>
-        </row>
-        <row r="30">
-          <cell r="A30"/>
-          <cell r="B30"/>
         </row>
       </sheetData>
       <sheetData sheetId="3"/>
@@ -783,13 +751,13 @@
       </c>
       <c r="E2" s="1">
         <f>VLOOKUP(F2,reference!A:B,2,FALSE)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
         <v>-1</v>
@@ -798,10 +766,10 @@
         <v>-1</v>
       </c>
       <c r="J2" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -859,7 +827,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H4" s="1">
         <v>101</v>
@@ -894,7 +862,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="1">
         <v>102</v>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3247E6B-7F17-4606-B9BF-9E123A9F7A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A930EF6D-AE10-4DE6-875A-BC1713E52275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="-14610" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -410,8 +410,52 @@
             <v>2300</v>
           </cell>
           <cell r="B21" t="str">
-            <v>巻物</v>
-          </cell>
+            <v>部屋31ダメ巻物</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>2301</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>範囲50ダメ</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23"/>
+          <cell r="B23"/>
+        </row>
+        <row r="24">
+          <cell r="A24"/>
+          <cell r="B24"/>
+        </row>
+        <row r="25">
+          <cell r="A25"/>
+          <cell r="B25"/>
+        </row>
+        <row r="26">
+          <cell r="A26"/>
+          <cell r="B26"/>
+        </row>
+        <row r="27">
+          <cell r="A27"/>
+          <cell r="B27"/>
+        </row>
+        <row r="28">
+          <cell r="A28"/>
+          <cell r="B28"/>
+        </row>
+        <row r="29">
+          <cell r="A29"/>
+          <cell r="B29"/>
+        </row>
+        <row r="30">
+          <cell r="A30"/>
+          <cell r="B30"/>
+        </row>
+        <row r="31">
+          <cell r="A31"/>
+          <cell r="B31"/>
         </row>
       </sheetData>
       <sheetData sheetId="3"/>
@@ -684,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -743,6 +787,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="1">
+        <f>2000+A2</f>
         <v>2000</v>
       </c>
       <c r="D2" s="1" t="str">
@@ -778,6 +823,7 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1">
+        <f t="shared" ref="C3:C10" si="0">2000+A3</f>
         <v>2001</v>
       </c>
       <c r="D3" s="1" t="str">
@@ -813,6 +859,7 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1">
+        <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="D4" s="1" t="str">
@@ -848,6 +895,7 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1">
+        <f t="shared" si="0"/>
         <v>2101</v>
       </c>
       <c r="D5" s="1" t="str">
@@ -883,6 +931,7 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1">
+        <f t="shared" si="0"/>
         <v>2102</v>
       </c>
       <c r="D6" s="1" t="str">
@@ -918,6 +967,7 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1">
+        <f t="shared" si="0"/>
         <v>2103</v>
       </c>
       <c r="D7" s="1" t="str">
@@ -953,6 +1003,7 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1">
+        <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="D8" s="1" t="str">
@@ -980,6 +1031,78 @@
       </c>
       <c r="K8" s="1">
         <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="1">
+        <v>300</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>2300</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>VLOOKUP(C9,[1]Item!$A:$B,2,FALSE)</f>
+        <v>部屋31ダメ巻物</v>
+      </c>
+      <c r="E9" s="1">
+        <f>VLOOKUP(F9,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1">
+        <v>301</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1">
+        <f t="shared" si="0"/>
+        <v>2301</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>VLOOKUP(C10,[1]Item!$A:$B,2,FALSE)</f>
+        <v>範囲50ダメ</v>
+      </c>
+      <c r="E10" s="1">
+        <f>VLOOKUP(F10,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -993,7 +1116,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F8</xm:sqref>
+          <xm:sqref>F2:F10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A930EF6D-AE10-4DE6-875A-BC1713E52275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DC2A36-5768-48FC-A678-142952163A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="-14610" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="-14805" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -420,42 +420,6 @@
           <cell r="B22" t="str">
             <v>範囲50ダメ</v>
           </cell>
-        </row>
-        <row r="23">
-          <cell r="A23"/>
-          <cell r="B23"/>
-        </row>
-        <row r="24">
-          <cell r="A24"/>
-          <cell r="B24"/>
-        </row>
-        <row r="25">
-          <cell r="A25"/>
-          <cell r="B25"/>
-        </row>
-        <row r="26">
-          <cell r="A26"/>
-          <cell r="B26"/>
-        </row>
-        <row r="27">
-          <cell r="A27"/>
-          <cell r="B27"/>
-        </row>
-        <row r="28">
-          <cell r="A28"/>
-          <cell r="B28"/>
-        </row>
-        <row r="29">
-          <cell r="A29"/>
-          <cell r="B29"/>
-        </row>
-        <row r="30">
-          <cell r="A30"/>
-          <cell r="B30"/>
-        </row>
-        <row r="31">
-          <cell r="A31"/>
-          <cell r="B31"/>
         </row>
       </sheetData>
       <sheetData sheetId="3"/>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DC2A36-5768-48FC-A678-142952163A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819742AC-AD1D-419F-B201-00707AC09126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="-14805" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="-14340" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -330,7 +330,7 @@
             <v>2200</v>
           </cell>
           <cell r="B11" t="str">
-            <v>杖1</v>
+            <v>場所替えの杖</v>
           </cell>
         </row>
         <row r="12">
@@ -338,7 +338,7 @@
             <v>2201</v>
           </cell>
           <cell r="B12" t="str">
-            <v>杖2</v>
+            <v>雷の杖</v>
           </cell>
         </row>
         <row r="13">
@@ -346,7 +346,7 @@
             <v>2202</v>
           </cell>
           <cell r="B13" t="str">
-            <v>杖3</v>
+            <v>ワープの杖</v>
           </cell>
         </row>
         <row r="14">
@@ -354,7 +354,7 @@
             <v>2203</v>
           </cell>
           <cell r="B14" t="str">
-            <v>杖4</v>
+            <v>吹き飛ばしの杖</v>
           </cell>
         </row>
         <row r="15">
@@ -692,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C10" si="0">2000+A3</f>
+        <f t="shared" ref="C3:C13" si="0">2000+A3</f>
         <v>2001</v>
       </c>
       <c r="D3" s="1" t="str">
@@ -972,7 +972,7 @@
       </c>
       <c r="D8" s="1" t="str">
         <f>VLOOKUP(C8,[1]Item!$A:$B,2,FALSE)</f>
-        <v>杖1</v>
+        <v>場所替えの杖</v>
       </c>
       <c r="E8" s="1">
         <f>VLOOKUP(F8,reference!A:B,2,FALSE)</f>
@@ -982,7 +982,7 @@
         <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H8" s="1">
         <v>-1</v>
@@ -991,7 +991,7 @@
         <v>-1</v>
       </c>
       <c r="J8" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
         <v>7</v>
@@ -999,73 +999,181 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1">
+        <f t="shared" ref="C9" si="1">2000+A9</f>
+        <v>2201</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f>VLOOKUP(C9,[1]Item!$A:$B,2,FALSE)</f>
+        <v>雷の杖</v>
+      </c>
+      <c r="E9" s="1">
+        <f>VLOOKUP(F9,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="1">
+        <v>202</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1">
+        <f t="shared" ref="C10" si="2">2000+A10</f>
+        <v>2202</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f>VLOOKUP(C10,[1]Item!$A:$B,2,FALSE)</f>
+        <v>ワープの杖</v>
+      </c>
+      <c r="E10" s="1">
+        <f>VLOOKUP(F10,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+      <c r="K10" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1">
+        <v>203</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
+        <f t="shared" ref="C11" si="3">2000+A11</f>
+        <v>2203</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f>VLOOKUP(C11,[1]Item!$A:$B,2,FALSE)</f>
+        <v>吹き飛ばしの杖</v>
+      </c>
+      <c r="E11" s="1">
+        <f>VLOOKUP(F11,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="1">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>4</v>
+      </c>
+      <c r="K11" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1">
+        <v>300</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="D9" s="1" t="str">
-        <f>VLOOKUP(C9,[1]Item!$A:$B,2,FALSE)</f>
+      <c r="D12" s="1" t="str">
+        <f>VLOOKUP(C12,[1]Item!$A:$B,2,FALSE)</f>
         <v>部屋31ダメ巻物</v>
       </c>
-      <c r="E9" s="1">
-        <f>VLOOKUP(F9,reference!A:B,2,FALSE)</f>
+      <c r="E12" s="1">
+        <f>VLOOKUP(F12,reference!A:B,2,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G12" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="1">
+      <c r="H12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="1">
         <v>301</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>2301</v>
       </c>
-      <c r="D10" s="1" t="str">
-        <f>VLOOKUP(C10,[1]Item!$A:$B,2,FALSE)</f>
+      <c r="D13" s="1" t="str">
+        <f>VLOOKUP(C13,[1]Item!$A:$B,2,FALSE)</f>
         <v>範囲50ダメ</v>
       </c>
-      <c r="E10" s="1">
-        <f>VLOOKUP(F10,reference!A:B,2,FALSE)</f>
+      <c r="E13" s="1">
+        <f>VLOOKUP(F13,reference!A:B,2,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G13" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-1</v>
-      </c>
-      <c r="J10" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="H13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K13" s="1">
         <v>-1</v>
       </c>
     </row>
@@ -1080,7 +1188,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F10</xm:sqref>
+          <xm:sqref>F2:F13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819742AC-AD1D-419F-B201-00707AC09126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154A3DE7-D60A-4D3A-A3AD-17B47F90B2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="-14340" windowWidth="12390" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="-13485" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -240,10 +240,11 @@
       <sheetName val="Item"/>
       <sheetName val="Log"/>
       <sheetName val="Action"/>
+      <sheetName val="Trap"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="1">
           <cell r="A1" t="str">
@@ -266,7 +267,7 @@
             <v>2001</v>
           </cell>
           <cell r="B3" t="str">
-            <v>薬2</v>
+            <v>目薬</v>
           </cell>
         </row>
         <row r="4">
@@ -422,8 +423,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -775,10 +777,10 @@
         <v>-1</v>
       </c>
       <c r="J2" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="K2" s="1">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -792,7 +794,7 @@
       </c>
       <c r="D3" s="1" t="str">
         <f>VLOOKUP(C3,[1]Item!$A:$B,2,FALSE)</f>
-        <v>薬2</v>
+        <v>目薬</v>
       </c>
       <c r="E3" s="1">
         <f>VLOOKUP(F3,reference!A:B,2,FALSE)</f>
@@ -802,7 +804,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154A3DE7-D60A-4D3A-A3AD-17B47F90B2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABD0AB8-987F-4DF4-9C19-A4E3CA4CCFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="-13485" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -694,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -1179,6 +1179,42 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1">
+        <v>600</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1">
+        <f t="shared" ref="C14" si="4">2000+A14</f>
+        <v>2600</v>
+      </c>
+      <c r="D14" s="1" t="e">
+        <f>VLOOKUP(C14,[1]Item!$A:$B,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="1">
+        <f>VLOOKUP(F14,reference!A:B,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1190,7 +1226,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F13</xm:sqref>
+          <xm:sqref>F2:F14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
